--- a/sablonok/K ell sablon_sulyszam_minbizt_2024_12_v_1_0.xlsx
+++ b/sablonok/K ell sablon_sulyszam_minbizt_2024_12_v_1_0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Ugyfel\IKK_Innovatív_Képzéstámogató_Központ\IKKPQA03_GINOP_tananyag_QA\Munka\M01_tananyag_ellenorzes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_ROBOTOK\IKK-Robotok\IKK02_FormaiEllenorzesek\sablonok\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2137055F-1771-4965-A612-E1A1ABE11971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0AC0AA1-68A2-4EDF-B87C-29BE5BD4D683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EM X.Y" sheetId="2" r:id="rId1"/>
@@ -19,15 +19,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -338,7 +329,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -415,6 +406,13 @@
     <font>
       <sz val="14"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
@@ -1218,18 +1216,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I27"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="36.81640625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="9.1796875" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="9.81640625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="41.1796875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="60.54296875" style="5" customWidth="1"/>
+    <col min="1" max="1" width="36.77734375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="9.21875" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="9.77734375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="41.21875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="60.5546875" style="5" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="24.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1249,7 +1247,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
@@ -1275,7 +1273,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:9" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>6</v>
       </c>
@@ -1291,7 +1289,7 @@
       </c>
       <c r="H3" s="30"/>
     </row>
-    <row r="4" spans="1:9" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>42</v>
       </c>
@@ -1307,7 +1305,7 @@
       </c>
       <c r="H4" s="30"/>
     </row>
-    <row r="5" spans="1:9" s="2" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" s="2" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>12</v>
       </c>
@@ -1323,7 +1321,7 @@
       </c>
       <c r="H5" s="30"/>
     </row>
-    <row r="6" spans="1:9" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>50</v>
       </c>
@@ -1339,7 +1337,7 @@
       </c>
       <c r="H6" s="30"/>
     </row>
-    <row r="7" spans="1:9" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>20</v>
       </c>
@@ -1355,7 +1353,7 @@
       </c>
       <c r="H7" s="30"/>
     </row>
-    <row r="8" spans="1:9" s="2" customFormat="1" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" s="2" customFormat="1" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>16</v>
       </c>
@@ -1371,7 +1369,7 @@
       </c>
       <c r="H8" s="30"/>
     </row>
-    <row r="9" spans="1:9" s="2" customFormat="1" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" s="2" customFormat="1" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -1387,7 +1385,7 @@
       </c>
       <c r="H9" s="30"/>
     </row>
-    <row r="10" spans="1:9" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>33</v>
       </c>
@@ -1403,7 +1401,7 @@
       </c>
       <c r="H10" s="30"/>
     </row>
-    <row r="11" spans="1:9" s="2" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" s="2" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>27</v>
       </c>
@@ -1419,7 +1417,7 @@
       </c>
       <c r="H11" s="30"/>
     </row>
-    <row r="12" spans="1:9" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>53</v>
       </c>
@@ -1435,7 +1433,7 @@
       </c>
       <c r="H12" s="30"/>
     </row>
-    <row r="13" spans="1:9" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>52</v>
       </c>
@@ -1451,7 +1449,7 @@
       </c>
       <c r="H13" s="30"/>
     </row>
-    <row r="14" spans="1:9" ht="116" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A14" s="21" t="s">
         <v>29</v>
       </c>
@@ -1470,7 +1468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="92" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" ht="91.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="21" t="s">
         <v>28</v>
       </c>
@@ -1489,7 +1487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="58" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A16" s="21" t="s">
         <v>10</v>
       </c>
@@ -1508,7 +1506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="116" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A17" s="21" t="s">
         <v>11</v>
       </c>
@@ -1527,7 +1525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="145" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="144" x14ac:dyDescent="0.3">
       <c r="A18" s="21" t="s">
         <v>30</v>
       </c>
@@ -1546,7 +1544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="100" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="33" t="s">
         <v>22</v>
       </c>
@@ -1565,7 +1563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="174" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A20" s="13" t="s">
         <v>43</v>
       </c>
@@ -1584,7 +1582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="58" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
         <v>13</v>
       </c>
@@ -1603,7 +1601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
         <v>31</v>
       </c>
@@ -1622,7 +1620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
         <v>7</v>
       </c>
@@ -1641,7 +1639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="58" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
         <v>14</v>
       </c>
@@ -1660,7 +1658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
         <v>8</v>
       </c>
@@ -1679,7 +1677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="58" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A26" s="13" t="s">
         <v>9</v>
       </c>
@@ -1698,7 +1696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="87.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:8" ht="87.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="28" t="s">
         <v>15</v>
       </c>
@@ -1715,6 +1713,7 @@
     <mergeCell ref="B27:G27"/>
     <mergeCell ref="B1:F1"/>
   </mergeCells>
+  <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="B1">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>COUNTIF(D3:D13,"x")&gt;0</formula>
